--- a/resources/assistant/assistant.xlsx
+++ b/resources/assistant/assistant.xlsx
@@ -1380,20 +1380,16 @@
       <c r="X7" s="34" t="n"/>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="8">
-      <c r="A8" s="30" t="n"/>
+      <c r="A8" s="30" t="n">
+        <v>5</v>
+      </c>
       <c r="B8" s="30" t="n"/>
       <c r="C8" s="30" t="n"/>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>Icon_120_assistant_default.png</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>big_img_assistant_default.png</t>
-        </is>
-      </c>
+      <c r="D8" s="30" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E8" s="31" t="n"/>
+      <c r="F8" s="10" t="n"/>
       <c r="G8" s="30" t="n"/>
       <c r="H8" s="30" t="n"/>
       <c r="I8" s="30" t="n"/>
@@ -1414,19 +1410,98 @@
       <c r="X8" s="34" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1" s="8">
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
-      <c r="L9" s="17" t="n"/>
+      <c r="A9" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="30" t="n"/>
+      <c r="C9" s="30" t="n"/>
+      <c r="D9" s="30" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E9" s="31" t="n"/>
+      <c r="F9" s="31" t="n"/>
+      <c r="G9" s="30" t="n"/>
+      <c r="H9" s="30" t="n"/>
+      <c r="I9" s="30" t="n"/>
+      <c r="J9" s="30" t="n"/>
+      <c r="K9" s="30" t="n"/>
+      <c r="L9" s="30" t="n"/>
+      <c r="M9" s="32" t="n"/>
+      <c r="N9" s="32" t="n"/>
+      <c r="O9" s="32" t="n"/>
+      <c r="P9" s="32" t="n"/>
+      <c r="Q9" s="32" t="n"/>
+      <c r="R9" s="32" t="n"/>
+      <c r="S9" s="32" t="n"/>
+      <c r="T9" s="32" t="n"/>
+      <c r="U9" s="33" t="n"/>
+      <c r="V9" s="34" t="n"/>
+      <c r="W9" s="34" t="n"/>
+      <c r="X9" s="34" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="8">
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="L10" s="17" t="n"/>
+      <c r="A10" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="30" t="n"/>
+      <c r="C10" s="30" t="n"/>
+      <c r="D10" s="30" t="n">
+        <v>1031</v>
+      </c>
+      <c r="E10" s="31" t="n"/>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="30" t="n"/>
+      <c r="H10" s="30" t="n"/>
+      <c r="I10" s="30" t="n"/>
+      <c r="J10" s="30" t="n"/>
+      <c r="K10" s="30" t="n"/>
+      <c r="L10" s="30" t="n"/>
+      <c r="M10" s="32" t="n"/>
+      <c r="N10" s="32" t="n"/>
+      <c r="O10" s="32" t="n"/>
+      <c r="P10" s="32" t="n"/>
+      <c r="Q10" s="32" t="n"/>
+      <c r="R10" s="32" t="n"/>
+      <c r="S10" s="32" t="n"/>
+      <c r="T10" s="32" t="n"/>
+      <c r="U10" s="33" t="n"/>
+      <c r="V10" s="34" t="n"/>
+      <c r="W10" s="34" t="n"/>
+      <c r="X10" s="34" t="n"/>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="8">
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
-      <c r="L11" s="17" t="n"/>
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="30" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>Icon_120_assistant_default.png</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>big_img_assistant_default.png</t>
+        </is>
+      </c>
+      <c r="G11" s="30" t="n"/>
+      <c r="H11" s="30" t="n"/>
+      <c r="I11" s="30" t="n"/>
+      <c r="J11" s="30" t="n"/>
+      <c r="K11" s="30" t="n"/>
+      <c r="L11" s="30" t="n"/>
+      <c r="M11" s="32" t="n"/>
+      <c r="N11" s="32" t="n"/>
+      <c r="O11" s="32" t="n"/>
+      <c r="P11" s="32" t="n"/>
+      <c r="Q11" s="32" t="n"/>
+      <c r="R11" s="32" t="n"/>
+      <c r="S11" s="32" t="n"/>
+      <c r="T11" s="32" t="n"/>
+      <c r="U11" s="33" t="n"/>
+      <c r="V11" s="34" t="n"/>
+      <c r="W11" s="34" t="n"/>
+      <c r="X11" s="34" t="n"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="8">
       <c r="E12" s="14" t="n"/>

--- a/resources/assistant/assistant.xlsx
+++ b/resources/assistant/assistant.xlsx
@@ -1380,16 +1380,20 @@
       <c r="X7" s="34" t="n"/>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="8">
-      <c r="A8" s="30" t="n">
-        <v>5</v>
-      </c>
+      <c r="A8" s="30" t="n"/>
       <c r="B8" s="30" t="n"/>
       <c r="C8" s="30" t="n"/>
-      <c r="D8" s="30" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E8" s="31" t="n"/>
-      <c r="F8" s="10" t="n"/>
+      <c r="D8" s="30" t="n"/>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>Icon_120_assistant_default.png</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>big_img_assistant_default.png</t>
+        </is>
+      </c>
       <c r="G8" s="30" t="n"/>
       <c r="H8" s="30" t="n"/>
       <c r="I8" s="30" t="n"/>
@@ -1410,98 +1414,19 @@
       <c r="X8" s="34" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1" s="8">
-      <c r="A9" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="30" t="n"/>
-      <c r="C9" s="30" t="n"/>
-      <c r="D9" s="30" t="n">
-        <v>1030</v>
-      </c>
-      <c r="E9" s="31" t="n"/>
-      <c r="F9" s="31" t="n"/>
-      <c r="G9" s="30" t="n"/>
-      <c r="H9" s="30" t="n"/>
-      <c r="I9" s="30" t="n"/>
-      <c r="J9" s="30" t="n"/>
-      <c r="K9" s="30" t="n"/>
-      <c r="L9" s="30" t="n"/>
-      <c r="M9" s="32" t="n"/>
-      <c r="N9" s="32" t="n"/>
-      <c r="O9" s="32" t="n"/>
-      <c r="P9" s="32" t="n"/>
-      <c r="Q9" s="32" t="n"/>
-      <c r="R9" s="32" t="n"/>
-      <c r="S9" s="32" t="n"/>
-      <c r="T9" s="32" t="n"/>
-      <c r="U9" s="33" t="n"/>
-      <c r="V9" s="34" t="n"/>
-      <c r="W9" s="34" t="n"/>
-      <c r="X9" s="34" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="L9" s="17" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="8">
-      <c r="A10" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="30" t="n"/>
-      <c r="C10" s="30" t="n"/>
-      <c r="D10" s="30" t="n">
-        <v>1031</v>
-      </c>
-      <c r="E10" s="31" t="n"/>
-      <c r="F10" s="31" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="30" t="n"/>
-      <c r="I10" s="30" t="n"/>
-      <c r="J10" s="30" t="n"/>
-      <c r="K10" s="30" t="n"/>
-      <c r="L10" s="30" t="n"/>
-      <c r="M10" s="32" t="n"/>
-      <c r="N10" s="32" t="n"/>
-      <c r="O10" s="32" t="n"/>
-      <c r="P10" s="32" t="n"/>
-      <c r="Q10" s="32" t="n"/>
-      <c r="R10" s="32" t="n"/>
-      <c r="S10" s="32" t="n"/>
-      <c r="T10" s="32" t="n"/>
-      <c r="U10" s="33" t="n"/>
-      <c r="V10" s="34" t="n"/>
-      <c r="W10" s="34" t="n"/>
-      <c r="X10" s="34" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="L10" s="17" t="n"/>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="8">
-      <c r="A11" s="30" t="n"/>
-      <c r="B11" s="30" t="n"/>
-      <c r="C11" s="30" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="31" t="inlineStr">
-        <is>
-          <t>Icon_120_assistant_default.png</t>
-        </is>
-      </c>
-      <c r="F11" s="31" t="inlineStr">
-        <is>
-          <t>big_img_assistant_default.png</t>
-        </is>
-      </c>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="30" t="n"/>
-      <c r="I11" s="30" t="n"/>
-      <c r="J11" s="30" t="n"/>
-      <c r="K11" s="30" t="n"/>
-      <c r="L11" s="30" t="n"/>
-      <c r="M11" s="32" t="n"/>
-      <c r="N11" s="32" t="n"/>
-      <c r="O11" s="32" t="n"/>
-      <c r="P11" s="32" t="n"/>
-      <c r="Q11" s="32" t="n"/>
-      <c r="R11" s="32" t="n"/>
-      <c r="S11" s="32" t="n"/>
-      <c r="T11" s="32" t="n"/>
-      <c r="U11" s="33" t="n"/>
-      <c r="V11" s="34" t="n"/>
-      <c r="W11" s="34" t="n"/>
-      <c r="X11" s="34" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="L11" s="17" t="n"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="8">
       <c r="E12" s="14" t="n"/>
